--- a/data/trans_orig/P6607-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P6607-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la exposición a trabajos al aire libre en su trabajo en 2012</t>
+          <t>Población según la exposición a trabajos al aire libre en su trabajo en 2012 (tasa de respuesta: 99,14%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>73014</t>
+          <t>71516</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>102452</t>
+          <t>102234</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>38,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>100636</t>
+          <t>100177</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>125022</t>
+          <t>124517</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>62,84%</t>
+          <t>62,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>78,07%</t>
+          <t>77,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>180567</t>
+          <t>178015</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>221847</t>
+          <t>220690</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>42,19%</t>
+          <t>41,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,83%</t>
+          <t>51,56%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>44938</t>
+          <t>44818</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>74483</t>
+          <t>71704</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16296</t>
+          <t>15179</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>34871</t>
+          <t>33673</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>66843</t>
+          <t>66426</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>101246</t>
+          <t>99486</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>23,24%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>36907</t>
+          <t>37282</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>62175</t>
+          <t>62206</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6131</t>
+          <t>6071</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>20195</t>
+          <t>20257</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>45848</t>
+          <t>46843</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>75647</t>
+          <t>76322</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,83%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>59942</t>
+          <t>60777</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>91085</t>
+          <t>91592</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5929</t>
+          <t>5886</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20108</t>
+          <t>19911</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>68180</t>
+          <t>70119</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>102658</t>
+          <t>104670</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>24,45%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>144999</t>
+          <t>144325</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>187023</t>
+          <t>186806</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>35,61%</t>
+          <t>35,45%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>45,93%</t>
+          <t>45,88%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>180766</t>
+          <t>181364</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>210443</t>
+          <t>211230</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>66,82%</t>
+          <t>67,05%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>77,79%</t>
+          <t>78,09%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>337772</t>
+          <t>338443</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>388402</t>
+          <t>391723</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>49,84%</t>
+          <t>49,94%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>57,31%</t>
+          <t>57,8%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>66625</t>
+          <t>68004</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>100961</t>
+          <t>99620</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>35875</t>
+          <t>35260</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>61819</t>
+          <t>60014</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>108479</t>
+          <t>107178</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>149709</t>
+          <t>150277</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>22,18%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>58306</t>
+          <t>59881</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>91497</t>
+          <t>91700</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3980</t>
+          <t>3960</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17899</t>
+          <t>17582</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>66577</t>
+          <t>67658</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>99931</t>
+          <t>103118</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>15,22%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>68604</t>
+          <t>69526</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>102389</t>
+          <t>102410</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,7 +1655,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10887</t>
+          <t>9847</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>28178</t>
+          <t>27870</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>84667</t>
+          <t>83892</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>123828</t>
+          <t>123605</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,24%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>115211</t>
+          <t>116096</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>151634</t>
+          <t>151579</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>36,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>47,36%</t>
+          <t>47,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>137412</t>
+          <t>137675</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>166321</t>
+          <t>165783</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>64,11%</t>
+          <t>64,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,6%</t>
+          <t>77,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>261737</t>
+          <t>261960</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>311003</t>
+          <t>311995</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>48,97%</t>
+          <t>49,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>58,19%</t>
+          <t>58,37%</t>
         </is>
       </c>
     </row>
@@ -1983,12 +1983,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>49027</t>
+          <t>48849</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>80532</t>
+          <t>80527</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1998,7 +1998,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>25683</t>
+          <t>26359</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>49085</t>
+          <t>48907</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2033,12 +2033,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>80997</t>
+          <t>82485</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>118094</t>
+          <t>118605</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>22,19%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>48571</t>
+          <t>49752</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>78977</t>
+          <t>81857</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7567</t>
+          <t>7741</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25053</t>
+          <t>23433</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>61080</t>
+          <t>60315</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>97337</t>
+          <t>97624</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,26%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>45511</t>
+          <t>46457</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>75890</t>
+          <t>76568</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5923</t>
+          <t>5943</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>20321</t>
+          <t>21175</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>56489</t>
+          <t>55190</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>90052</t>
+          <t>87223</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,32%</t>
         </is>
       </c>
     </row>
@@ -2439,12 +2439,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>170813</t>
+          <t>171649</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>212600</t>
+          <t>213317</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2454,12 +2454,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>41,17%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>51,0%</t>
+          <t>51,17%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2474,12 +2474,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>210116</t>
+          <t>211333</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>242020</t>
+          <t>242352</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2489,12 +2489,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>69,69%</t>
+          <t>70,09%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>80,27%</t>
+          <t>80,38%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2509,12 +2509,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>392217</t>
+          <t>392312</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>445985</t>
+          <t>448119</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2524,12 +2524,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>54,6%</t>
+          <t>54,61%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>62,08%</t>
+          <t>62,38%</t>
         </is>
       </c>
     </row>
@@ -2552,12 +2552,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>80437</t>
+          <t>78373</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>112380</t>
+          <t>113187</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2587,12 +2587,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>32495</t>
+          <t>32706</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>57575</t>
+          <t>57377</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>117357</t>
+          <t>118603</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>160872</t>
+          <t>161580</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,49%</t>
         </is>
       </c>
     </row>
@@ -2665,12 +2665,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>59611</t>
+          <t>58518</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>91663</t>
+          <t>89308</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2680,12 +2680,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2700,12 +2700,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>9500</t>
+          <t>9854</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>25749</t>
+          <t>26921</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>75084</t>
+          <t>74271</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>110074</t>
+          <t>110543</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,39%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>42881</t>
+          <t>41665</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>71613</t>
+          <t>70164</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7953</t>
+          <t>7776</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>23485</t>
+          <t>22706</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>52670</t>
+          <t>52275</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>87838</t>
+          <t>86760</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,08%</t>
         </is>
       </c>
     </row>
@@ -3008,12 +3008,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>539460</t>
+          <t>540046</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>613819</t>
+          <t>615807</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>38,24%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>43,47%</t>
+          <t>43,61%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3043,12 +3043,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>661766</t>
+          <t>659481</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>718364</t>
+          <t>716899</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>69,92%</t>
+          <t>69,68%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>75,9%</t>
+          <t>75,74%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1214727</t>
+          <t>1216760</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1317617</t>
+          <t>1316405</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>51,5%</t>
+          <t>51,59%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>55,87%</t>
+          <t>55,81%</t>
         </is>
       </c>
     </row>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>266271</t>
+          <t>268030</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>332619</t>
+          <t>332366</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>130074</t>
+          <t>129340</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>176825</t>
+          <t>175282</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>410354</t>
+          <t>410417</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>489697</t>
+          <t>488004</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,7 +3211,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,69%</t>
         </is>
       </c>
     </row>
@@ -3234,12 +3234,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>231578</t>
+          <t>234360</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>291893</t>
+          <t>293645</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>37366</t>
+          <t>37145</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>68036</t>
+          <t>67265</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>279821</t>
+          <t>279964</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>347372</t>
+          <t>347201</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,72%</t>
         </is>
       </c>
     </row>
@@ -3347,12 +3347,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>246765</t>
+          <t>244837</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>304392</t>
+          <t>307204</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>40806</t>
+          <t>40413</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>70279</t>
+          <t>69093</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>292255</t>
+          <t>289413</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>362058</t>
+          <t>360075</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3432,12 +3432,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,27%</t>
         </is>
       </c>
     </row>
@@ -3614,7 +3614,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la exposición a trabajos al aire libre en su trabajo en 2016</t>
+          <t>Población según la exposición a trabajos al aire libre en su trabajo en 2016 (tasa de respuesta: 99,53%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3809,12 +3809,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>83648</t>
+          <t>84860</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>114485</t>
+          <t>115681</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3824,12 +3824,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>34,54%</t>
+          <t>35,04%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>47,27%</t>
+          <t>47,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3844,12 +3844,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>103733</t>
+          <t>104312</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>125960</t>
+          <t>126448</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>62,31%</t>
+          <t>62,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>75,66%</t>
+          <t>75,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3879,12 +3879,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>196110</t>
+          <t>194569</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>237431</t>
+          <t>235271</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>47,99%</t>
+          <t>47,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>58,1%</t>
+          <t>57,57%</t>
         </is>
       </c>
     </row>
@@ -3922,12 +3922,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>38556</t>
+          <t>38158</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>63835</t>
+          <t>64274</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24051</t>
+          <t>23767</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>43390</t>
+          <t>42710</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>67985</t>
+          <t>67497</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>99340</t>
+          <t>98909</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,2%</t>
         </is>
       </c>
     </row>
@@ -4035,12 +4035,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>34292</t>
+          <t>34067</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>58077</t>
+          <t>58142</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2584</t>
+          <t>2670</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11815</t>
+          <t>13309</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>39576</t>
+          <t>40053</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>66739</t>
+          <t>66631</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,3%</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>36986</t>
+          <t>35784</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>60573</t>
+          <t>62138</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6774</t>
+          <t>7077</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19861</t>
+          <t>20783</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>45432</t>
+          <t>44766</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>73303</t>
+          <t>75752</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>18,54%</t>
         </is>
       </c>
     </row>
@@ -4378,12 +4378,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>122667</t>
+          <t>124650</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>162802</t>
+          <t>163476</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4393,12 +4393,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>39,94%</t>
+          <t>40,1%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>182571</t>
+          <t>182293</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>212168</t>
+          <t>211152</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>66,69%</t>
+          <t>66,59%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>77,5%</t>
+          <t>77,13%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>315015</t>
+          <t>314077</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>368384</t>
+          <t>368113</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4463,12 +4463,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>46,23%</t>
+          <t>46,09%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>54,06%</t>
+          <t>54,02%</t>
         </is>
       </c>
     </row>
@@ -4491,12 +4491,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>87890</t>
+          <t>87531</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>125184</t>
+          <t>124720</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>29762</t>
+          <t>29238</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>54060</t>
+          <t>54178</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4541,12 +4541,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>124385</t>
+          <t>124667</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>170277</t>
+          <t>170422</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4576,12 +4576,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>25,01%</t>
         </is>
       </c>
     </row>
@@ -4604,12 +4604,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>45538</t>
+          <t>46681</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>76775</t>
+          <t>78105</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9202</t>
+          <t>9512</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>25514</t>
+          <t>26416</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4654,12 +4654,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>59398</t>
+          <t>58441</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>95783</t>
+          <t>95211</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4689,12 +4689,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>13,97%</t>
         </is>
       </c>
     </row>
@@ -4717,12 +4717,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>81336</t>
+          <t>82256</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>118146</t>
+          <t>117010</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4732,12 +4732,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>11723</t>
+          <t>12126</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>28173</t>
+          <t>29831</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4767,12 +4767,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>98292</t>
+          <t>99158</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>139967</t>
+          <t>141352</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4802,12 +4802,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,74%</t>
         </is>
       </c>
     </row>
@@ -4947,12 +4947,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>92761</t>
+          <t>92084</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>130473</t>
+          <t>130008</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4962,12 +4962,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>35,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>135404</t>
+          <t>134866</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>168163</t>
+          <t>166455</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4997,12 +4997,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>50,05%</t>
+          <t>49,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>62,15%</t>
+          <t>61,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>236261</t>
+          <t>238938</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>287707</t>
+          <t>290039</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5032,12 +5032,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>37,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>45,43%</t>
+          <t>45,8%</t>
         </is>
       </c>
     </row>
@@ -5060,12 +5060,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>101171</t>
+          <t>98256</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>135997</t>
+          <t>137203</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5075,12 +5075,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>37,83%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>65868</t>
+          <t>66317</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>97741</t>
+          <t>94776</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5110,12 +5110,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>36,13%</t>
+          <t>35,03%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>174481</t>
+          <t>172347</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>223489</t>
+          <t>221344</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>35,29%</t>
+          <t>34,95%</t>
         </is>
       </c>
     </row>
@@ -5173,12 +5173,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>45442</t>
+          <t>44167</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>77538</t>
+          <t>75029</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5208,12 +5208,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13469</t>
+          <t>13251</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>30590</t>
+          <t>29451</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5223,12 +5223,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>63401</t>
+          <t>62799</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>98365</t>
+          <t>97320</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5258,12 +5258,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,37%</t>
         </is>
       </c>
     </row>
@@ -5286,12 +5286,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>58072</t>
+          <t>59575</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>90804</t>
+          <t>92453</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5301,12 +5301,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5321,12 +5321,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10753</t>
+          <t>11305</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>28309</t>
+          <t>28572</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5336,12 +5336,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5356,12 +5356,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>76312</t>
+          <t>75898</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>112675</t>
+          <t>113302</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5371,12 +5371,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,89%</t>
         </is>
       </c>
     </row>
@@ -5516,12 +5516,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>170572</t>
+          <t>171860</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>210968</t>
+          <t>211860</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5531,12 +5531,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>42,72%</t>
+          <t>43,04%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>52,83%</t>
+          <t>53,06%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5551,12 +5551,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>238887</t>
+          <t>238722</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>269186</t>
+          <t>268578</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5566,12 +5566,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>73,62%</t>
+          <t>73,57%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>82,96%</t>
+          <t>82,77%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5586,12 +5586,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>417653</t>
+          <t>421206</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>471202</t>
+          <t>472775</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5601,12 +5601,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>57,7%</t>
+          <t>58,19%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>65,1%</t>
+          <t>65,32%</t>
         </is>
       </c>
     </row>
@@ -5629,12 +5629,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>72493</t>
+          <t>71786</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>105920</t>
+          <t>105340</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5644,12 +5644,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5664,12 +5664,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>27935</t>
+          <t>28602</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>51445</t>
+          <t>51392</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5699,12 +5699,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>109601</t>
+          <t>105901</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>148532</t>
+          <t>147417</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5714,12 +5714,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,37%</t>
         </is>
       </c>
     </row>
@@ -5742,12 +5742,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>49248</t>
+          <t>48655</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>78116</t>
+          <t>78632</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5757,12 +5757,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5777,12 +5777,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>13775</t>
+          <t>13767</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>31447</t>
+          <t>31977</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5792,12 +5792,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5812,12 +5812,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>67601</t>
+          <t>68588</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>102108</t>
+          <t>103565</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,31%</t>
         </is>
       </c>
     </row>
@@ -5855,12 +5855,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>42815</t>
+          <t>43592</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>70751</t>
+          <t>72351</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5870,12 +5870,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5890,12 +5890,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4581</t>
+          <t>3976</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>17682</t>
+          <t>17567</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5925,12 +5925,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>51845</t>
+          <t>50692</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>82770</t>
+          <t>82314</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,37%</t>
         </is>
       </c>
     </row>
@@ -6085,12 +6085,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>506671</t>
+          <t>508040</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>584108</t>
+          <t>581427</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6100,12 +6100,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>41,18%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6120,12 +6120,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>689865</t>
+          <t>690314</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>746907</t>
+          <t>748661</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6135,12 +6135,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>66,63%</t>
+          <t>66,68%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>72,14%</t>
+          <t>72,31%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6155,12 +6155,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1214293</t>
+          <t>1216608</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1308733</t>
+          <t>1316116</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6170,12 +6170,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>49,62%</t>
+          <t>49,72%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>53,48%</t>
+          <t>53,78%</t>
         </is>
       </c>
     </row>
@@ -6198,12 +6198,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>325486</t>
+          <t>328787</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>396758</t>
+          <t>395988</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6213,12 +6213,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6233,12 +6233,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>169017</t>
+          <t>168542</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>219304</t>
+          <t>219340</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6268,12 +6268,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>511582</t>
+          <t>516810</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>595566</t>
+          <t>599167</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,48%</t>
         </is>
       </c>
     </row>
@@ -6311,12 +6311,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>199267</t>
+          <t>201614</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>259207</t>
+          <t>259652</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6326,12 +6326,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6346,12 +6346,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>50812</t>
+          <t>49049</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>80108</t>
+          <t>79149</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>259230</t>
+          <t>260269</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>324161</t>
+          <t>324340</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6396,7 +6396,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -6424,12 +6424,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>247712</t>
+          <t>248389</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>311315</t>
+          <t>308930</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6439,12 +6439,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6459,12 +6459,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>45840</t>
+          <t>45228</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>75603</t>
+          <t>75326</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>302003</t>
+          <t>302411</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>371426</t>
+          <t>369739</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,11%</t>
         </is>
       </c>
     </row>
@@ -6691,7 +6691,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la exposición a trabajos al aire libre en su trabajo en 2023</t>
+          <t>Población según la exposición a trabajos al aire libre en su trabajo en 2023 (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6886,12 +6886,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>31727</t>
+          <t>31042</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>56869</t>
+          <t>58265</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6901,12 +6901,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6921,12 +6921,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>65299</t>
+          <t>65897</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>84703</t>
+          <t>84596</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6936,12 +6936,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>52,51%</t>
+          <t>52,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>68,11%</t>
+          <t>68,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6956,12 +6956,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>102931</t>
+          <t>102713</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>136974</t>
+          <t>137792</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6971,12 +6971,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>34,71%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>46,19%</t>
+          <t>46,47%</t>
         </is>
       </c>
     </row>
@@ -6999,12 +6999,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>38871</t>
+          <t>38131</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>64894</t>
+          <t>66253</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7014,12 +7014,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,69%</t>
+          <t>38,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7034,12 +7034,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13635</t>
+          <t>13090</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>27718</t>
+          <t>26746</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>54594</t>
+          <t>57210</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>85771</t>
+          <t>88372</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>29,8%</t>
         </is>
       </c>
     </row>
@@ -7112,12 +7112,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14723</t>
+          <t>14813</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>36173</t>
+          <t>36313</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7127,12 +7127,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7147,12 +7147,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6295</t>
+          <t>6080</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>17061</t>
+          <t>17234</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>24292</t>
+          <t>23281</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>48313</t>
+          <t>46632</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>15,73%</t>
         </is>
       </c>
     </row>
@@ -7225,12 +7225,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>41451</t>
+          <t>40331</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>69966</t>
+          <t>69639</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7240,12 +7240,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>40,45%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7260,12 +7260,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12657</t>
+          <t>12902</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27696</t>
+          <t>27068</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>58078</t>
+          <t>57392</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>91821</t>
+          <t>92424</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>31,17%</t>
         </is>
       </c>
     </row>
@@ -7455,12 +7455,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>42487</t>
+          <t>45797</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>241144</t>
+          <t>245396</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7470,12 +7470,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>44,44%</t>
+          <t>45,23%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7490,12 +7490,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>119880</t>
+          <t>120888</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>143661</t>
+          <t>144125</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>59,16%</t>
+          <t>59,66%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>70,9%</t>
+          <t>71,13%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>110454</t>
+          <t>119142</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>395924</t>
+          <t>395233</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>53,13%</t>
+          <t>53,04%</t>
         </is>
       </c>
     </row>
@@ -7568,12 +7568,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>22294</t>
+          <t>18989</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>123924</t>
+          <t>126037</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7583,12 +7583,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7603,12 +7603,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>36194</t>
+          <t>36203</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>55773</t>
+          <t>56403</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>44419</t>
+          <t>44589</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>169461</t>
+          <t>170554</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,89%</t>
         </is>
       </c>
     </row>
@@ -7681,12 +7681,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15226</t>
+          <t>15812</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>102199</t>
+          <t>101476</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7696,12 +7696,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7716,12 +7716,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5893</t>
+          <t>5946</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17597</t>
+          <t>19514</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>22390</t>
+          <t>23398</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>97176</t>
+          <t>99079</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,3%</t>
         </is>
       </c>
     </row>
@@ -7794,12 +7794,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>93446</t>
+          <t>93025</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>456325</t>
+          <t>455742</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7809,12 +7809,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>84,1%</t>
+          <t>83,99%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7829,12 +7829,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>9008</t>
+          <t>9424</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>21002</t>
+          <t>20886</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7844,12 +7844,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7864,12 +7864,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>96861</t>
+          <t>98768</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>562140</t>
+          <t>554218</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7879,12 +7879,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>75,43%</t>
+          <t>74,37%</t>
         </is>
       </c>
     </row>
@@ -8024,12 +8024,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>48765</t>
+          <t>47671</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>74312</t>
+          <t>75680</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8039,12 +8039,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>27,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>43,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8059,12 +8059,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>55570</t>
+          <t>54551</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>134236</t>
+          <t>134707</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>33,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,4%</t>
+          <t>81,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>107840</t>
+          <t>116335</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>191865</t>
+          <t>191364</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>56,87%</t>
+          <t>56,73%</t>
         </is>
       </c>
     </row>
@@ -8137,12 +8137,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>38337</t>
+          <t>39146</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>65343</t>
+          <t>66265</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8152,12 +8152,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>37,89%</t>
+          <t>38,43%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8172,12 +8172,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>15509</t>
+          <t>15996</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>103234</t>
+          <t>103078</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8187,12 +8187,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>62,6%</t>
+          <t>62,51%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8207,12 +8207,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>67059</t>
+          <t>68285</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>179686</t>
+          <t>174837</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8222,12 +8222,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>53,26%</t>
+          <t>51,83%</t>
         </is>
       </c>
     </row>
@@ -8250,12 +8250,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>21072</t>
+          <t>20634</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>46682</t>
+          <t>45600</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8265,12 +8265,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8285,12 +8285,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3109</t>
+          <t>3166</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14942</t>
+          <t>14283</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8300,12 +8300,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8320,12 +8320,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>25252</t>
+          <t>25441</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>55590</t>
+          <t>56354</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8335,12 +8335,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,71%</t>
         </is>
       </c>
     </row>
@@ -8363,12 +8363,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18208</t>
+          <t>18122</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>40537</t>
+          <t>41368</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8378,12 +8378,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8398,12 +8398,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1635</t>
+          <t>1636</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10862</t>
+          <t>11164</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8418,7 +8418,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8433,12 +8433,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>21736</t>
+          <t>20485</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>47685</t>
+          <t>46968</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8448,12 +8448,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>13,92%</t>
         </is>
       </c>
     </row>
@@ -8593,12 +8593,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>120834</t>
+          <t>120374</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>151256</t>
+          <t>151790</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8608,12 +8608,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>53,52%</t>
+          <t>53,31%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>66,99%</t>
+          <t>67,23%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8628,12 +8628,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>144098</t>
+          <t>143917</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>161975</t>
+          <t>161918</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>76,63%</t>
+          <t>76,53%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>86,13%</t>
+          <t>86,1%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8663,12 +8663,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>270664</t>
+          <t>269176</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>308191</t>
+          <t>309194</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8678,12 +8678,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>65,4%</t>
+          <t>65,04%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>74,47%</t>
+          <t>74,71%</t>
         </is>
       </c>
     </row>
@@ -8706,12 +8706,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>31494</t>
+          <t>30780</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>55746</t>
+          <t>55634</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8721,12 +8721,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8741,12 +8741,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>17476</t>
+          <t>17499</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>33237</t>
+          <t>33239</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8756,12 +8756,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8776,12 +8776,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>53254</t>
+          <t>52951</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>83659</t>
+          <t>84751</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8791,12 +8791,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>20,48%</t>
         </is>
       </c>
     </row>
@@ -8819,12 +8819,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>18200</t>
+          <t>17276</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>39275</t>
+          <t>39115</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8854,12 +8854,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2040</t>
+          <t>2033</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>8651</t>
+          <t>8831</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8874,7 +8874,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8889,12 +8889,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>22074</t>
+          <t>21854</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>43868</t>
+          <t>43547</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8904,12 +8904,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,52%</t>
         </is>
       </c>
     </row>
@@ -8932,12 +8932,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>12946</t>
+          <t>12669</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>30069</t>
+          <t>31262</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8967,12 +8967,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2229</t>
+          <t>2202</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>10625</t>
+          <t>10038</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8982,12 +8982,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9002,12 +9002,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>17087</t>
+          <t>17339</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>36029</t>
+          <t>36580</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9017,12 +9017,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,84%</t>
         </is>
       </c>
     </row>
@@ -9162,12 +9162,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>179497</t>
+          <t>208745</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>483755</t>
+          <t>483375</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>43,46%</t>
+          <t>43,43%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9197,12 +9197,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>393808</t>
+          <t>365120</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>498104</t>
+          <t>498252</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9212,12 +9212,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>57,92%</t>
+          <t>53,7%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>73,26%</t>
+          <t>73,28%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9232,12 +9232,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>539710</t>
+          <t>552664</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>981182</t>
+          <t>990896</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9247,12 +9247,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>54,72%</t>
+          <t>55,27%</t>
         </is>
       </c>
     </row>
@@ -9275,12 +9275,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>113441</t>
+          <t>113770</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>279186</t>
+          <t>279671</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9310,12 +9310,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>104829</t>
+          <t>101706</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>225167</t>
+          <t>245332</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9325,12 +9325,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9345,12 +9345,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>227840</t>
+          <t>224103</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>429608</t>
+          <t>439479</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9360,12 +9360,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>24,51%</t>
         </is>
       </c>
     </row>
@@ -9388,12 +9388,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>63850</t>
+          <t>73875</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>178651</t>
+          <t>179885</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9403,12 +9403,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9423,12 +9423,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>23999</t>
+          <t>24321</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>44164</t>
+          <t>45277</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9438,12 +9438,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9458,12 +9458,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>103627</t>
+          <t>105177</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>207605</t>
+          <t>209816</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9473,12 +9473,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,7%</t>
         </is>
       </c>
     </row>
@@ -9501,12 +9501,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>193167</t>
+          <t>193105</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>741629</t>
+          <t>695128</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9516,12 +9516,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>66,63%</t>
+          <t>62,46%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -9536,12 +9536,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>32120</t>
+          <t>33124</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>55746</t>
+          <t>55349</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9551,12 +9551,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -9571,12 +9571,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>223928</t>
+          <t>221107</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>911621</t>
+          <t>918309</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -9586,12 +9586,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>50,85%</t>
+          <t>51,22%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P6607-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P6607-Habitat-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>71516</t>
+          <t>72285</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>102234</t>
+          <t>104217</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,16%</t>
+          <t>38,91%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>100177</t>
+          <t>100843</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>124517</t>
+          <t>123915</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>62,56%</t>
+          <t>62,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>77,76%</t>
+          <t>77,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>178015</t>
+          <t>180276</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>220690</t>
+          <t>223148</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>41,59%</t>
+          <t>42,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,56%</t>
+          <t>52,14%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>44818</t>
+          <t>45267</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>71704</t>
+          <t>72129</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15179</t>
+          <t>16215</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>33673</t>
+          <t>34784</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>66426</t>
+          <t>65282</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>99486</t>
+          <t>98699</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>23,06%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>37282</t>
+          <t>37541</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>62206</t>
+          <t>62737</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6071</t>
+          <t>5977</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>20257</t>
+          <t>18917</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>46843</t>
+          <t>47428</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>76322</t>
+          <t>75247</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,58%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>60777</t>
+          <t>59973</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>91592</t>
+          <t>89231</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,19%</t>
+          <t>33,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5886</t>
+          <t>5891</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19911</t>
+          <t>19574</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>70119</t>
+          <t>69254</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>104670</t>
+          <t>102776</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>24,01%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>144325</t>
+          <t>144979</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>186806</t>
+          <t>189221</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>35,61%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>45,88%</t>
+          <t>46,47%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>181364</t>
+          <t>181339</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>211230</t>
+          <t>210881</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>67,05%</t>
+          <t>67,04%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>78,09%</t>
+          <t>77,96%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>338443</t>
+          <t>336030</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>391723</t>
+          <t>390011</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>49,94%</t>
+          <t>49,59%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>57,8%</t>
+          <t>57,55%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>68004</t>
+          <t>66892</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>99620</t>
+          <t>99686</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>35260</t>
+          <t>35470</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>60014</t>
+          <t>59234</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,47 +1464,47 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
+          <t>21,9%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>128451</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>107578</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>150353</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>18,95%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>15,87%</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
           <t>22,19%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>128451</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>107178</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>150277</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>18,95%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>15,82%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>22,18%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>59881</t>
+          <t>58727</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>91700</t>
+          <t>90230</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3960</t>
+          <t>3983</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17582</t>
+          <t>16809</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>67658</t>
+          <t>66354</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>103118</t>
+          <t>101875</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,03%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>69526</t>
+          <t>68072</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>102410</t>
+          <t>103150</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>9847</t>
+          <t>10238</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>27870</t>
+          <t>28825</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>83892</t>
+          <t>83245</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>123605</t>
+          <t>123729</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,26%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>116096</t>
+          <t>115624</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>151579</t>
+          <t>152589</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>36,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>47,34%</t>
+          <t>47,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>137675</t>
+          <t>137625</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>165783</t>
+          <t>166200</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>64,23%</t>
+          <t>64,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,35%</t>
+          <t>77,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>261960</t>
+          <t>262503</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>311995</t>
+          <t>311822</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>49,01%</t>
+          <t>49,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>58,37%</t>
+          <t>58,34%</t>
         </is>
       </c>
     </row>
@@ -1983,12 +1983,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>48849</t>
+          <t>49639</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>80527</t>
+          <t>79360</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1998,12 +1998,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>26359</t>
+          <t>25965</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>48907</t>
+          <t>48660</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2033,12 +2033,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>82485</t>
+          <t>82009</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>118605</t>
+          <t>120611</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,56%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>49752</t>
+          <t>50038</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>81857</t>
+          <t>80613</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7741</t>
+          <t>6952</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>23433</t>
+          <t>24107</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>60315</t>
+          <t>60651</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>97624</t>
+          <t>95817</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>17,93%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>46457</t>
+          <t>47478</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>76568</t>
+          <t>76990</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5943</t>
+          <t>5898</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>21175</t>
+          <t>21003</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>55190</t>
+          <t>55189</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>87223</t>
+          <t>88731</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,7 +2299,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,6%</t>
         </is>
       </c>
     </row>
@@ -2439,12 +2439,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>171649</t>
+          <t>171690</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>213317</t>
+          <t>213320</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>41,17%</t>
+          <t>41,18%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2474,12 +2474,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>211333</t>
+          <t>210428</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>242352</t>
+          <t>242075</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2489,12 +2489,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>70,09%</t>
+          <t>69,79%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>80,38%</t>
+          <t>80,29%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2509,12 +2509,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>392312</t>
+          <t>390616</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>448119</t>
+          <t>444495</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2524,12 +2524,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>54,61%</t>
+          <t>54,37%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>62,38%</t>
+          <t>61,87%</t>
         </is>
       </c>
     </row>
@@ -2552,12 +2552,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>78373</t>
+          <t>79230</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>113187</t>
+          <t>114198</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2587,12 +2587,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>32706</t>
+          <t>32338</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>57377</t>
+          <t>57310</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>118603</t>
+          <t>119349</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>161580</t>
+          <t>163373</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,74%</t>
         </is>
       </c>
     </row>
@@ -2665,12 +2665,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>58518</t>
+          <t>59115</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>89308</t>
+          <t>89855</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2680,12 +2680,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2700,12 +2700,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>9854</t>
+          <t>9199</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>26921</t>
+          <t>26335</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>74271</t>
+          <t>74342</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>110543</t>
+          <t>110156</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,33%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>41665</t>
+          <t>41613</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>70164</t>
+          <t>70838</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7776</t>
+          <t>7784</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>22706</t>
+          <t>22406</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>52275</t>
+          <t>54648</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>86760</t>
+          <t>87807</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,22%</t>
         </is>
       </c>
     </row>
@@ -3008,12 +3008,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>540046</t>
+          <t>541129</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>615807</t>
+          <t>614118</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>38,32%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>43,61%</t>
+          <t>43,49%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3043,12 +3043,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>659481</t>
+          <t>660305</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>716899</t>
+          <t>715033</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>69,68%</t>
+          <t>69,76%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>75,74%</t>
+          <t>75,55%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1216760</t>
+          <t>1216187</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1316405</t>
+          <t>1316115</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>51,59%</t>
+          <t>51,56%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>55,81%</t>
+          <t>55,8%</t>
         </is>
       </c>
     </row>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>268030</t>
+          <t>266271</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>332366</t>
+          <t>333099</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>129340</t>
+          <t>129885</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>175282</t>
+          <t>174736</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>410417</t>
+          <t>408509</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>488004</t>
+          <t>489544</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,76%</t>
         </is>
       </c>
     </row>
@@ -3234,12 +3234,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>234360</t>
+          <t>231893</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>293645</t>
+          <t>291650</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>37145</t>
+          <t>37633</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>67265</t>
+          <t>67307</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3284,7 +3284,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>279964</t>
+          <t>282063</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>347201</t>
+          <t>348803</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,79%</t>
         </is>
       </c>
     </row>
@@ -3347,12 +3347,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>244837</t>
+          <t>241382</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>307204</t>
+          <t>306903</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>40413</t>
+          <t>40082</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>69093</t>
+          <t>70524</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>289413</t>
+          <t>294535</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>360075</t>
+          <t>360604</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3432,12 +3432,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,29%</t>
         </is>
       </c>
     </row>
@@ -3809,12 +3809,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>84860</t>
+          <t>84989</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>115681</t>
+          <t>115089</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3824,12 +3824,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>47,77%</t>
+          <t>47,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3844,12 +3844,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>104312</t>
+          <t>103046</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>126448</t>
+          <t>126694</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>62,65%</t>
+          <t>61,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>75,95%</t>
+          <t>76,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3879,12 +3879,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>194569</t>
+          <t>193916</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>235271</t>
+          <t>236229</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>47,61%</t>
+          <t>47,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>57,57%</t>
+          <t>57,8%</t>
         </is>
       </c>
     </row>
@@ -3922,12 +3922,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>38158</t>
+          <t>37486</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>64274</t>
+          <t>62662</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23767</t>
+          <t>23680</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>42710</t>
+          <t>43501</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>67497</t>
+          <t>66238</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>98909</t>
+          <t>99755</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,41%</t>
         </is>
       </c>
     </row>
@@ -4035,12 +4035,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>34067</t>
+          <t>33931</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>58142</t>
+          <t>58406</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2670</t>
+          <t>2597</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13309</t>
+          <t>12363</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>40053</t>
+          <t>38820</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>66631</t>
+          <t>64611</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>15,81%</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>35784</t>
+          <t>34953</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>62138</t>
+          <t>61008</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7077</t>
+          <t>6612</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20783</t>
+          <t>19222</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>44766</t>
+          <t>45878</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>75752</t>
+          <t>73801</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,06%</t>
         </is>
       </c>
     </row>
@@ -4378,12 +4378,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>124650</t>
+          <t>123677</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>163476</t>
+          <t>163443</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>30,34%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>182293</t>
+          <t>182995</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>211152</t>
+          <t>212448</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>66,59%</t>
+          <t>66,84%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>77,13%</t>
+          <t>77,6%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>314077</t>
+          <t>313873</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>368113</t>
+          <t>368630</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4463,12 +4463,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>46,09%</t>
+          <t>46,06%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>54,02%</t>
+          <t>54,1%</t>
         </is>
       </c>
     </row>
@@ -4491,12 +4491,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>87531</t>
+          <t>87629</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>124720</t>
+          <t>124876</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>29238</t>
+          <t>29807</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>54178</t>
+          <t>53161</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4541,12 +4541,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>124667</t>
+          <t>124130</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>170422</t>
+          <t>170199</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4576,12 +4576,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>24,98%</t>
         </is>
       </c>
     </row>
@@ -4604,12 +4604,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>46681</t>
+          <t>46104</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>78105</t>
+          <t>77857</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9512</t>
+          <t>9788</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>26416</t>
+          <t>25881</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4654,12 +4654,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>58441</t>
+          <t>60118</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>95211</t>
+          <t>97445</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4689,12 +4689,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>14,3%</t>
         </is>
       </c>
     </row>
@@ -4717,12 +4717,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>82256</t>
+          <t>80014</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>117010</t>
+          <t>116237</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4732,12 +4732,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>12126</t>
+          <t>12123</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>29831</t>
+          <t>28554</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>99158</t>
+          <t>97489</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>141352</t>
+          <t>138402</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4802,12 +4802,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,31%</t>
         </is>
       </c>
     </row>
@@ -4947,12 +4947,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>92084</t>
+          <t>92689</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>130008</t>
+          <t>130043</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4962,12 +4962,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>35,84%</t>
+          <t>35,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>134866</t>
+          <t>132469</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>166455</t>
+          <t>166448</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>49,85%</t>
+          <t>48,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>238938</t>
+          <t>236441</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>290039</t>
+          <t>289815</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5032,12 +5032,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>37,73%</t>
+          <t>37,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>45,8%</t>
+          <t>45,77%</t>
         </is>
       </c>
     </row>
@@ -5060,12 +5060,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>98256</t>
+          <t>101632</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>137203</t>
+          <t>137613</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5075,12 +5075,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>37,94%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>66317</t>
+          <t>65371</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>94776</t>
+          <t>97603</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5110,12 +5110,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>36,07%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>172347</t>
+          <t>172942</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>221344</t>
+          <t>221050</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>34,91%</t>
         </is>
       </c>
     </row>
@@ -5173,12 +5173,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>44167</t>
+          <t>46084</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>75029</t>
+          <t>75042</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5188,7 +5188,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -5208,12 +5208,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13251</t>
+          <t>13536</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>29451</t>
+          <t>30669</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5223,12 +5223,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>62799</t>
+          <t>63729</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>97320</t>
+          <t>97248</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5258,12 +5258,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,36%</t>
         </is>
       </c>
     </row>
@@ -5286,12 +5286,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>59575</t>
+          <t>59832</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>92453</t>
+          <t>92098</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5301,12 +5301,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5321,12 +5321,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11305</t>
+          <t>11075</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>28572</t>
+          <t>29139</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5336,12 +5336,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5356,12 +5356,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>75898</t>
+          <t>76413</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>113302</t>
+          <t>112173</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5371,12 +5371,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>17,71%</t>
         </is>
       </c>
     </row>
@@ -5516,12 +5516,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>171860</t>
+          <t>172015</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>211860</t>
+          <t>211810</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5531,12 +5531,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>43,04%</t>
+          <t>43,08%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>53,06%</t>
+          <t>53,04%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5551,12 +5551,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>238722</t>
+          <t>239513</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>268578</t>
+          <t>270119</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5566,12 +5566,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>73,57%</t>
+          <t>73,81%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>82,77%</t>
+          <t>83,25%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5586,12 +5586,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>421206</t>
+          <t>418682</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>472775</t>
+          <t>470253</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5601,12 +5601,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>58,19%</t>
+          <t>57,85%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>65,32%</t>
+          <t>64,97%</t>
         </is>
       </c>
     </row>
@@ -5629,12 +5629,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>71786</t>
+          <t>73462</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>105340</t>
+          <t>106641</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5644,12 +5644,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5664,12 +5664,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>28602</t>
+          <t>26819</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>51392</t>
+          <t>51348</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5699,12 +5699,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>105901</t>
+          <t>107435</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>147417</t>
+          <t>148125</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5714,12 +5714,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,47%</t>
         </is>
       </c>
     </row>
@@ -5742,12 +5742,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>48655</t>
+          <t>49994</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>78632</t>
+          <t>78462</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5757,12 +5757,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5777,12 +5777,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>13767</t>
+          <t>14158</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>31977</t>
+          <t>33028</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5792,12 +5792,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5812,12 +5812,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>68588</t>
+          <t>67994</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>103565</t>
+          <t>102132</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,11%</t>
         </is>
       </c>
     </row>
@@ -5855,12 +5855,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>43592</t>
+          <t>43697</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>72351</t>
+          <t>70919</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5870,12 +5870,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5890,12 +5890,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3976</t>
+          <t>4706</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>17567</t>
+          <t>17150</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5925,12 +5925,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>50692</t>
+          <t>50716</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>82314</t>
+          <t>82381</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,38%</t>
         </is>
       </c>
     </row>
@@ -6085,12 +6085,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>508040</t>
+          <t>506868</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>581427</t>
+          <t>585366</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6100,12 +6100,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>41,18%</t>
+          <t>41,46%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6120,12 +6120,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>690314</t>
+          <t>689611</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>748661</t>
+          <t>751952</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6135,12 +6135,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>66,68%</t>
+          <t>66,61%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>72,31%</t>
+          <t>72,63%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6155,12 +6155,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1216608</t>
+          <t>1213629</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1316116</t>
+          <t>1316703</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6170,12 +6170,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>49,72%</t>
+          <t>49,59%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>53,78%</t>
+          <t>53,81%</t>
         </is>
       </c>
     </row>
@@ -6198,12 +6198,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>328787</t>
+          <t>330127</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>395988</t>
+          <t>398178</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6213,12 +6213,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6233,12 +6233,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>168542</t>
+          <t>170059</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>219340</t>
+          <t>218211</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6268,12 +6268,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>516810</t>
+          <t>509085</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>599167</t>
+          <t>595963</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>24,35%</t>
         </is>
       </c>
     </row>
@@ -6311,12 +6311,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>201614</t>
+          <t>199717</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>259652</t>
+          <t>261724</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6326,12 +6326,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6346,12 +6346,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>49049</t>
+          <t>49021</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>79149</t>
+          <t>80186</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>260269</t>
+          <t>258213</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>324340</t>
+          <t>325542</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,3%</t>
         </is>
       </c>
     </row>
@@ -6424,12 +6424,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>248389</t>
+          <t>243643</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>308930</t>
+          <t>304874</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6439,12 +6439,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6459,12 +6459,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>45228</t>
+          <t>44228</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>75326</t>
+          <t>74571</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>302411</t>
+          <t>303733</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>369739</t>
+          <t>373183</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,25%</t>
         </is>
       </c>
     </row>
@@ -6881,32 +6881,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>43795</t>
+          <t>48301</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>31042</t>
+          <t>36097</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>58265</t>
+          <t>64644</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>33,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6916,32 +6916,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>75462</t>
+          <t>80753</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>65897</t>
+          <t>70517</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>84596</t>
+          <t>90182</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>60,68%</t>
+          <t>58,79%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>52,99%</t>
+          <t>51,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>68,03%</t>
+          <t>65,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6951,32 +6951,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>119257</t>
+          <t>129054</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>102713</t>
+          <t>109889</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>137792</t>
+          <t>148659</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>40,22%</t>
+          <t>39,01%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>33,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>46,47%</t>
+          <t>44,93%</t>
         </is>
       </c>
     </row>
@@ -6994,32 +6994,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>51293</t>
+          <t>56477</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>38131</t>
+          <t>43047</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>66253</t>
+          <t>72715</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
+          <t>37,59%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7029,32 +7029,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>19311</t>
+          <t>22075</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13090</t>
+          <t>15369</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>26746</t>
+          <t>29871</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7064,32 +7064,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>70603</t>
+          <t>78552</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>57210</t>
+          <t>62850</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>88372</t>
+          <t>95495</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>28,86%</t>
         </is>
       </c>
     </row>
@@ -7107,32 +7107,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>23251</t>
+          <t>27122</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14813</t>
+          <t>17916</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>36313</t>
+          <t>41913</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7142,32 +7142,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>10614</t>
+          <t>11180</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6080</t>
+          <t>6576</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>17234</t>
+          <t>17105</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7177,32 +7177,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>33865</t>
+          <t>38301</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>23281</t>
+          <t>27711</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>46632</t>
+          <t>53903</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>16,29%</t>
         </is>
       </c>
     </row>
@@ -7220,32 +7220,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>53832</t>
+          <t>61567</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>40331</t>
+          <t>46730</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>69639</t>
+          <t>76898</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>31,82%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,45%</t>
+          <t>39,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>18970</t>
+          <t>23362</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12902</t>
+          <t>16272</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27068</t>
+          <t>32967</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>72802</t>
+          <t>84928</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>57392</t>
+          <t>66758</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>92424</t>
+          <t>102030</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>30,84%</t>
         </is>
       </c>
     </row>
@@ -7333,17 +7333,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>172171</t>
+          <t>193467</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>172171</t>
+          <t>193467</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>172171</t>
+          <t>193467</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7368,17 +7368,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>124356</t>
+          <t>137369</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>124356</t>
+          <t>137369</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>124356</t>
+          <t>137369</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7403,17 +7403,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>296527</t>
+          <t>330836</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>296527</t>
+          <t>330836</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>296527</t>
+          <t>330836</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7450,32 +7450,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>126080</t>
+          <t>137696</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>45797</t>
+          <t>117687</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>245396</t>
+          <t>157541</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>41,31%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>35,31%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>45,23%</t>
+          <t>47,27%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7485,32 +7485,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>132514</t>
+          <t>142786</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>120888</t>
+          <t>129892</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>144125</t>
+          <t>155356</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>65,4%</t>
+          <t>64,7%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>59,66%</t>
+          <t>58,86%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>71,13%</t>
+          <t>70,4%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7520,32 +7520,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>258595</t>
+          <t>280481</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>119142</t>
+          <t>252353</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>395233</t>
+          <t>304073</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>34,7%</t>
+          <t>50,63%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>45,55%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>53,04%</t>
+          <t>54,89%</t>
         </is>
       </c>
     </row>
@@ -7563,32 +7563,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>64353</t>
+          <t>69432</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18989</t>
+          <t>54885</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>126037</t>
+          <t>85984</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>45382</t>
+          <t>49269</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>36203</t>
+          <t>39543</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>56403</t>
+          <t>60762</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>109735</t>
+          <t>118700</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>44589</t>
+          <t>100062</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>170554</t>
+          <t>138538</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>25,01%</t>
         </is>
       </c>
     </row>
@@ -7676,32 +7676,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>51483</t>
+          <t>55962</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15812</t>
+          <t>42570</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>101476</t>
+          <t>72602</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7711,32 +7711,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>10523</t>
+          <t>12302</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5946</t>
+          <t>6802</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>19514</t>
+          <t>20556</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>62006</t>
+          <t>68263</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>23398</t>
+          <t>52696</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>99079</t>
+          <t>87960</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>15,88%</t>
         </is>
       </c>
     </row>
@@ -7789,32 +7789,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>300687</t>
+          <t>70203</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>93025</t>
+          <t>55646</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>455742</t>
+          <t>90251</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>55,42%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7824,32 +7824,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>14204</t>
+          <t>16321</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>9424</t>
+          <t>10612</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>20886</t>
+          <t>23632</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7859,32 +7859,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>314891</t>
+          <t>86524</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>98768</t>
+          <t>70072</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>554218</t>
+          <t>107386</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>42,25%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>74,37%</t>
+          <t>19,38%</t>
         </is>
       </c>
     </row>
@@ -7902,17 +7902,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>542603</t>
+          <t>333292</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>542603</t>
+          <t>333292</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>542603</t>
+          <t>333292</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7937,17 +7937,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>202623</t>
+          <t>220677</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>202623</t>
+          <t>220677</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>202623</t>
+          <t>220677</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7972,17 +7972,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>745227</t>
+          <t>553968</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>745227</t>
+          <t>553968</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>745227</t>
+          <t>553968</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8019,32 +8019,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>61013</t>
+          <t>63996</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>47671</t>
+          <t>49377</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>75680</t>
+          <t>79920</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>43,89%</t>
+          <t>39,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8054,32 +8054,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>104540</t>
+          <t>121812</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>54551</t>
+          <t>112076</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>134707</t>
+          <t>129933</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>63,39%</t>
+          <t>79,27%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>72,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,68%</t>
+          <t>84,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>165552</t>
+          <t>185808</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>116335</t>
+          <t>164842</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>191364</t>
+          <t>205672</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>49,07%</t>
+          <t>52,04%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>46,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>56,73%</t>
+          <t>57,6%</t>
         </is>
       </c>
     </row>
@@ -8132,32 +8132,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>51506</t>
+          <t>62046</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>39146</t>
+          <t>46027</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>66265</t>
+          <t>77344</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>38,43%</t>
+          <t>38,03%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8167,32 +8167,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>47732</t>
+          <t>17425</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>15996</t>
+          <t>11593</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>103078</t>
+          <t>24592</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>62,51%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8202,32 +8202,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>99238</t>
+          <t>79471</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>68285</t>
+          <t>63340</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>174837</t>
+          <t>98705</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>51,83%</t>
+          <t>27,64%</t>
         </is>
       </c>
     </row>
@@ -8245,32 +8245,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>31538</t>
+          <t>37035</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>20634</t>
+          <t>25045</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>45600</t>
+          <t>53810</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8280,32 +8280,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>7879</t>
+          <t>9376</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3166</t>
+          <t>4867</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14283</t>
+          <t>15569</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8315,32 +8315,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>39417</t>
+          <t>46411</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>25441</t>
+          <t>33726</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>56354</t>
+          <t>62223</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>17,43%</t>
         </is>
       </c>
     </row>
@@ -8358,32 +8358,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>28380</t>
+          <t>40301</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18122</t>
+          <t>27492</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>41368</t>
+          <t>59564</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8393,32 +8393,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4760</t>
+          <t>5054</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1636</t>
+          <t>1956</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11164</t>
+          <t>10948</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8428,32 +8428,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>33140</t>
+          <t>45355</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>20485</t>
+          <t>30418</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>46968</t>
+          <t>63559</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>17,8%</t>
         </is>
       </c>
     </row>
@@ -8471,17 +8471,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>172436</t>
+          <t>203379</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>172436</t>
+          <t>203379</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>172436</t>
+          <t>203379</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8506,17 +8506,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>164911</t>
+          <t>153667</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>164911</t>
+          <t>153667</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>164911</t>
+          <t>153667</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8541,17 +8541,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>337347</t>
+          <t>357046</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>337347</t>
+          <t>357046</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>337347</t>
+          <t>357046</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8588,32 +8588,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>135755</t>
+          <t>148832</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>120374</t>
+          <t>132915</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>151790</t>
+          <t>165782</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>60,13%</t>
+          <t>59,98%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>53,31%</t>
+          <t>53,57%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>67,23%</t>
+          <t>66,82%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8623,32 +8623,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>153639</t>
+          <t>169761</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>143917</t>
+          <t>158671</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>161918</t>
+          <t>179113</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>81,7%</t>
+          <t>81,36%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>76,53%</t>
+          <t>76,04%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>86,1%</t>
+          <t>85,84%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8658,32 +8658,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>289394</t>
+          <t>318593</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>269176</t>
+          <t>298481</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>309194</t>
+          <t>337827</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>69,93%</t>
+          <t>69,75%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>65,04%</t>
+          <t>65,34%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>74,71%</t>
+          <t>73,96%</t>
         </is>
       </c>
     </row>
@@ -8701,32 +8701,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>42715</t>
+          <t>42190</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>30780</t>
+          <t>30618</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>55634</t>
+          <t>56316</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8736,32 +8736,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>24504</t>
+          <t>28246</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>17499</t>
+          <t>20339</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>33239</t>
+          <t>38857</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8771,32 +8771,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>67219</t>
+          <t>70435</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>52951</t>
+          <t>55858</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>84751</t>
+          <t>87089</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>19,07%</t>
         </is>
       </c>
     </row>
@@ -8814,32 +8814,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>26769</t>
+          <t>31301</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>17276</t>
+          <t>20933</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>39115</t>
+          <t>43111</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8849,32 +8849,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4671</t>
+          <t>5283</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2033</t>
+          <t>2226</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>8831</t>
+          <t>10210</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8884,32 +8884,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>31440</t>
+          <t>36584</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>21854</t>
+          <t>25869</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>43547</t>
+          <t>50496</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>11,05%</t>
         </is>
       </c>
     </row>
@@ -8927,32 +8927,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>20547</t>
+          <t>25796</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>12669</t>
+          <t>16375</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>31262</t>
+          <t>37024</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8962,32 +8962,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>5240</t>
+          <t>5375</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2202</t>
+          <t>2311</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>10038</t>
+          <t>11340</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8997,32 +8997,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>25787</t>
+          <t>31171</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>17339</t>
+          <t>22146</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>36580</t>
+          <t>43757</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>9,58%</t>
         </is>
       </c>
     </row>
@@ -9040,17 +9040,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>225786</t>
+          <t>248119</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>225786</t>
+          <t>248119</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>225786</t>
+          <t>248119</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9075,17 +9075,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>188054</t>
+          <t>208665</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>188054</t>
+          <t>208665</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>188054</t>
+          <t>208665</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9110,17 +9110,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>413840</t>
+          <t>456784</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>413840</t>
+          <t>456784</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>413840</t>
+          <t>456784</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9157,32 +9157,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>366644</t>
+          <t>398826</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>208745</t>
+          <t>365424</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>483375</t>
+          <t>434101</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>40,77%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>37,35%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>43,43%</t>
+          <t>44,37%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9192,32 +9192,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>466154</t>
+          <t>515112</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>365120</t>
+          <t>494051</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>498252</t>
+          <t>536914</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>68,56%</t>
+          <t>71,51%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>53,7%</t>
+          <t>68,58%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>73,28%</t>
+          <t>74,53%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9227,32 +9227,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>832798</t>
+          <t>913937</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>552664</t>
+          <t>871720</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>990896</t>
+          <t>954335</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>46,45%</t>
+          <t>53,8%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>51,32%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>55,27%</t>
+          <t>56,18%</t>
         </is>
       </c>
     </row>
@@ -9270,32 +9270,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>209866</t>
+          <t>230145</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>113770</t>
+          <t>202082</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>279671</t>
+          <t>261093</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9305,32 +9305,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>136929</t>
+          <t>117014</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>101706</t>
+          <t>99516</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>245332</t>
+          <t>134205</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9340,32 +9340,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>346795</t>
+          <t>347159</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>224103</t>
+          <t>314004</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>439479</t>
+          <t>383578</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>22,58%</t>
         </is>
       </c>
     </row>
@@ -9383,32 +9383,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>133041</t>
+          <t>151420</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>73875</t>
+          <t>127968</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>179885</t>
+          <t>176395</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9418,32 +9418,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>33687</t>
+          <t>38140</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>24321</t>
+          <t>28548</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>45277</t>
+          <t>50862</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9453,32 +9453,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>166728</t>
+          <t>189560</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>105177</t>
+          <t>161946</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>209816</t>
+          <t>220357</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>12,97%</t>
         </is>
       </c>
     </row>
@@ -9496,32 +9496,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>403446</t>
+          <t>197866</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>193105</t>
+          <t>169159</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>695128</t>
+          <t>229166</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>62,46%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -9531,32 +9531,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>43174</t>
+          <t>50112</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>33124</t>
+          <t>37828</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>55349</t>
+          <t>62793</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -9566,32 +9566,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>446619</t>
+          <t>247978</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>221107</t>
+          <t>218257</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>918309</t>
+          <t>282131</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>51,22%</t>
+          <t>16,61%</t>
         </is>
       </c>
     </row>
@@ -9609,17 +9609,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1112997</t>
+          <t>978257</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1112997</t>
+          <t>978257</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1112997</t>
+          <t>978257</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -9644,17 +9644,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>679944</t>
+          <t>720378</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>679944</t>
+          <t>720378</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>679944</t>
+          <t>720378</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -9679,17 +9679,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1792941</t>
+          <t>1698635</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1792941</t>
+          <t>1698635</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1792941</t>
+          <t>1698635</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
